--- a/Dashboard Tracker.xlsx
+++ b/Dashboard Tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="47" min="1" max="1"/>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="M14" s="16">
@@ -2152,6 +2152,12 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A6:P6"/>

--- a/Dashboard Tracker.xlsx
+++ b/Dashboard Tracker.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="47" min="1" max="1"/>
@@ -749,7 +749,7 @@
     <row r="2" ht="19.5" customHeight="1" s="47">
       <c r="A2" s="46" t="inlineStr">
         <is>
-          <t>Ministry Brands  |  Shelby Financials  |  Step 1 of 6 Complete – Purpose Documents Done</t>
+          <t>Ministry Brands  |  Shelby Financials  |  Steps 1-5 Complete for all buildable widgets - awaiting Step 6 sign-off</t>
         </is>
       </c>
     </row>
@@ -1501,22 +1501,22 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="M15" s="23">
@@ -1527,7 +1527,7 @@
       <c r="O15" s="24" t="n"/>
       <c r="P15" s="25" t="inlineStr">
         <is>
-          <t>21 configurable queries — DB tables per query TBC</t>
+          <t>21 configurable queries — DB tables per query TBC; Completed by Jo (her build) - out of scope for this project, never ported or modified (per direct instruction 2026-09-07)</t>
         </is>
       </c>
     </row>
@@ -1570,17 +1570,17 @@
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -1639,17 +1639,17 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -1920,17 +1920,17 @@
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="M21" s="10">
@@ -1941,7 +1941,7 @@
       <c r="O21" s="11" t="n"/>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>System-controlled tiles; up to 8 navigation links; no user config</t>
+          <t>System-controlled tiles; up to 8 navigation links; no user config; Completed by Jo (her build) - out of scope for this project, never ported or modified (per direct instruction 2026-09-07)</t>
         </is>
       </c>
     </row>
@@ -1984,17 +1984,17 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -2053,17 +2053,17 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -2152,12 +2152,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A6:P6"/>
